--- a/data/daily/2026-09/2026-09-29.xlsx
+++ b/data/daily/2026-09/2026-09-29.xlsx
@@ -1195,14 +1195,114 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1317,67 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,160 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="342900" cy="457200"/>
+    <ext cx="457200" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1450,207 +1450,207 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2596,28 +2596,12 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16146</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>피로 회복 및 활력 충전 — 피곤할 때 섭취 시 활력이 생기고 컨디션 관리에 도움이 됨</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>선물용으로 높은 만족도 — 30대 생일이나 명절 선물로 주고받기 적합함</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>간편한 복용 방식 — 액상과 정제를 함께 섭취하는 구성이라 간편함</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>가격 부담 — 매일 장기간 섭취하기에는 가격이 다소 부담스러움</t>
-        </is>
-      </c>
+        <v>16147</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
@@ -2659,23 +2643,11 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15479</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>빠른 배송 및 깔끔한 포장 — 연휴 기간에도 배송이 빠르고 패키지가 고급스러움</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>피로 회복 효과 — 시험 준비나 피로할 때 섭취 시 피로 해소에 도움이 됨</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>휴대 및 복용 편의성 — 하나씩 들고 다니며 부담 없이 먹기 좋음</t>
-        </is>
-      </c>
+        <v>15480</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -2718,28 +2690,12 @@
         <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>3370</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>활력 증진 및 피로 개선 — 힘든 일을 할 때 생기가 생기고 피곤함이 줄어듦</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>선물 만족도 — 가족이나 지인에게 선물하기 좋으며 받는 사람의 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>쿠폰 할인 혜택 — 할인 쿠폰을 적용하여 알뜰하게 구매 가능함</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>쇼핑백 상태 불량 — 선물용으로 함께 제공된 쇼핑백의 품질이 불량함</t>
-        </is>
-      </c>
+        <v>3371</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -2783,26 +2739,10 @@
       <c r="J5" t="n">
         <v>796</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>체력 방전 예방 — 육아나 힘든 일 전에 먹으면 하루 종일 에너지를 유지하는 데 도움 됨</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>개별 포장의 편리성 — 한 포씩 포장되어 가방이나 책상에 두고 챙겨 먹기 편함</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>빠른 배송과 가격 — 배송이 빠르고 저렴한 가격에 구매 가능함</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>배송 요청 사항 미반영 — 관리실 위탁 요청에도 문 앞에 배송되어 아쉬움</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
@@ -2846,21 +2786,9 @@
       <c r="J6" t="n">
         <v>1696</v>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>빠른 활력 충전 — 섭취 후 피로가 감소하고 즉각적인 활력이 느껴짐</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>상큼한 맛과 편의성 — 맛이 상큼해서 목넘김이 좋고 마시기 편리함</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>신속한 배송 — 주문 후 배송이 매우 빠르게 도착함</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -2876,60 +2804,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>"한국인 맞춤 명품 비타민" 옵티젠 이뮨 멀티비타민&amp;미네랄 30입 / 1박스</t>
+          <t>[센트룸] 맛있는 멀티비타민 미네랄 멀티구미 (80구미)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>옵티젠</t>
+          <t>센트룸</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>59,900원</t>
+          <t>24,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11090567</t>
+          <t>https://gift.kakao.com/product/7320451</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260928083206_e0dd807ea02f482d93440e2a32dfd08d.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260901110153_bb9a8b1870e2492e99dbbf1747444c66.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>214</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>정성스러운 선물 포장 — 선물 패키징이 정성스럽고 깔끔하여 받는 기분이 좋음</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>피로 개선 효과 — 꾸준히 섭취 시 덜 피로하고 컨디션 유지에 좋음</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>간편한 1일 섭취 — 캡슐과 액상을 한 번에 복용할 수 있어 사무실 등에서 챙겨 먹기 편함</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>포장재 오염 상태 — 택배 상자와 쇼핑백에 먼지가 묻어 도착함</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>밀봉 스티커 훼손 — 스티커가 반쯤 떼어져 있고 손자국과 이물질이 남아 있음</t>
-        </is>
-      </c>
+        <v>6489</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
@@ -2943,50 +2851,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[센트룸] 맛있는 멀티비타민 미네랄 멀티구미 (80구미)</t>
+          <t>"한국인 맞춤 명품 비타민" 옵티젠 이뮨 멀티비타민&amp;미네랄 30입 / 1박스</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>센트룸</t>
+          <t>옵티젠</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24,000원</t>
+          <t>59,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7320451</t>
+          <t>https://gift.kakao.com/product/11090567</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260901110153_bb9a8b1870e2492e99dbbf1747444c66.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260928083206_e0dd807ea02f482d93440e2a32dfd08d.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>6489</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>맛있는 젤리 제형 — 마이구미처럼 맛있고 물 없이 편하게 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>꾸준한 복용 편의성 — 거부감 없는 맛과 제형 덕분에 매일 잊지 않고 챙겨 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>귀여운 패키지 포장 — 포장이 귀엽고 깔끔하여 부담 없는 선물로 적합함</t>
-        </is>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -3031,21 +2927,9 @@
       <c r="J9" t="n">
         <v>8729</v>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>물 없는 간편 섭취 — 액상과 정제가 함께 있어 물 없이 어디서나 먹기 편함</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>활력 증진 효과 — 피곤할 때 섭취 시 에너지가 생기는 느낌을 받음</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>개별 포장 및 디자인 — 휴대하기 편한 개별 포장에 케이스 디자인이 예쁨</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -3053,7 +2937,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -3061,50 +2945,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병</t>
+          <t>'성별 맞춤 설계' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>52,900원</t>
+          <t>59,800원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10903147</t>
+          <t>https://gift.kakao.com/product/8167919</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260928130637_4b5e189e4cc74b40bc33bd3c75d10253.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260928090417_28fb45c20b10424fb6c1bd6211e4e4e9.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>780</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>간편한 복용과 휴대성 — 먹기 편리하며 챙겨 다니기 용이함</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>빠른 배송 및 쇼핑백 증정 — 연휴에도 배송이 빠르고 쇼핑백이 포함되어 선물하기 좋음</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>넉넉한 용량 구성 — 한 달 분량의 알찬 구성으로 든든하게 섭취 가능함</t>
-        </is>
-      </c>
+        <v>773</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -3112,7 +2984,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -3120,55 +2992,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>'성별 맞춤 설계' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>59,800원</t>
+          <t>52,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/8167919</t>
+          <t>https://gift.kakao.com/product/10903147</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260928090417_28fb45c20b10424fb6c1bd6211e4e4e9.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260928130637_4b5e189e4cc74b40bc33bd3c75d10253.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>773</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>성별 맞춤 선택 — 남성용과 여성용을 선택하여 구매할 수 있음</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>피로 완화 지속성 — 꾸준히 먹으면 피로감이 줄어들고 활력이 오래 유지됨</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>휴대 및 복용 편의성 — 휴대하기 편하고 챙겨 먹기 간편함</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>알약 크기 부담 — 기존 제품 대비 알약 크기가 커서 삼키기 다소 힘듦</t>
-        </is>
-      </c>
+        <v>780</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -3210,28 +3066,12 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>745</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>고급스러운 포장 — 틴케이스와 보자기 등 패키지가 매우 예쁘고 정성스러움</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>비리지 않은 맛 — 특유의 비린 맛이 없고 상큼해서 맛이 좋음</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>낱개 앰플 섭취 편의 — 앰플 형태로 하나씩 따서 간편하게 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>비싼 가격대 — 가격대가 다소 높은 편이며 점차 인상됨</t>
-        </is>
-      </c>
+        <v>747</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
     </row>
@@ -3273,23 +3113,11 @@
         <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>1681</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>소화 촉진 및 속 편안함 — 식후 복용 시 소화에 도움이 되고 속이 편안해짐</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>부담 없는 맛 — 거부감이나 불편함이 없는 고구마 맛임</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>빠른 배송과 풍부한 사은품 — 배송이 빠르고 추가 사은품 구성이 좋음</t>
-        </is>
-      </c>
+        <v>1682</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -3334,31 +3162,11 @@
       <c r="J14" t="n">
         <v>152</v>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>높은 포만감과 맛 — 하나만 먹어도 포만감이 크고 맛이 좋음</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>다양한 구성과 사은품 — 여러 종류를 맛볼 수 있으며 증정 보냉백 디자인이 예쁨</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>할인 혜택과 빠른 발송 — 할인 행사로 가격 만족도가 높고 발송이 빠름</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>오배송 문제 — 주문한 구성과 달리 일부 제품이 누락되거나 중복 배송됨</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>포장 터짐 및 헐렁함 — 제품 일부가 터져 소스가 묻거나 진공 포장이 불량함</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
     </row>
     <row r="15" ht="38" customHeight="1">
@@ -3399,28 +3207,12 @@
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>58</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>뛰어난 가성비 — 할인가로 구매 시 가성비가 매우 훌륭함</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>부드러운 식감과 다양한 맛 — 닭가슴살이 부드럽고 종류가 다양해 질리지 않음</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>꼼꼼한 포장과 배송 — 포장 상태가 꼼꼼하며 빠르게 도착함</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>배송 중 해동 발생 — 배송 도착 시 제품이 모두 녹아서 도착함</t>
-        </is>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
     </row>
@@ -3464,33 +3256,17 @@
       <c r="J16" t="n">
         <v>104</v>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>맛있는 베리말차 맛 — 효소가 고소하고 맛있어 꾸준히 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>더부룩함 개선 — 식후 복용 시 더부룩함이 줄어들고 속이 편안해짐</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>만족스러운 사은품 구성 — 포토카드 및 단백질바 증정품 구성이 우수함</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>배송 지연 및 사은품 하자 — 배송이 다소 늦고 초기 증정 포토카드에 하자가 있었음</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="B17" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3498,50 +3274,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>셀렉스</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>28,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13550266</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>215</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>비리지 않은 깔끔한 맛 — 단백질 특유의 텁텁함이나 비린 맛없이 달달하고 깔끔함</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>운동 후 영양 보충 — 운동 후나 허기질 때 간편하게 챙겨 먹기 적합함</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>빠른 배송 서비스 — 배송이 빠르고 증정품 서비스가 제공됨</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
@@ -3549,7 +3313,7 @@
     <row r="18" ht="38" customHeight="1">
       <c r="B18" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3557,50 +3321,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>아일로 타입1 콜라겐 비오틴 앰플 14일분 오간자 에디션 (고급 오간자 패키징 + 선물용 쇼핑백)</t>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>32,900원</t>
+          <t>28,900원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965673</t>
+          <t>https://gift.kakao.com/product/13550266</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260928091204_17479341408f44afb805d97625daff01.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>759</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>고급스러운 패키지 — 포장이 예쁘고 케이스 디자인이 고급스러움</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>상큼하고 맛있는 음료 제형 — 새콤하고 맛있어서 약을 싫어하는 사람도 먹기 편함</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>선물용 만족도 — 받았을 때 기분 좋은 선물용 구성임</t>
-        </is>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -3608,7 +3360,7 @@
     <row r="19" ht="38" customHeight="1">
       <c r="B19" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3616,50 +3368,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+          <t>아일로 타입1 콜라겐 비오틴 앰플 14일분 오간자 에디션 (고급 오간자 패키징 + 선물용 쇼핑백)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>32,900원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7556791</t>
+          <t>https://gift.kakao.com/product/4965673</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260928091204_17479341408f44afb805d97625daff01.jpg</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>1534</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>체감 피로 개선 — 아침 복용 및 운동 전 섭취 시 피로감이 줄고 활력이 생김</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>알찬 영양제 조합 — 아르기닌과 밀크씨슬 또는 마카를 한 번에 챙길 수 있음</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>쇼핑백 증정 — 쇼핑백이 포함되어 있어 선물용으로 전달하기 깔끔함</t>
-        </is>
-      </c>
+        <v>759</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -3667,7 +3407,7 @@
     <row r="20" ht="38" customHeight="1">
       <c r="B20" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3675,50 +3415,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>33,200원</t>
+          <t>25,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12064702</t>
+          <t>https://gift.kakao.com/product/7556791</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>18</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>고급스러운 선물 세트 포장 — 보라색 패키지와 쇼핑백 포장이 고급스러움</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>숙취 완화 효과 — 음주 전후 섭취 시 다음 날 피로와 숙취가 줄어듦</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>스틱형 휴대성 — 소형 스틱형 개별 포장이라 물 없이 휴대 및 섭취가 간편함</t>
-        </is>
-      </c>
+        <v>1534</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
@@ -3763,26 +3491,10 @@
       <c r="J21" t="n">
         <v>11</v>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>상큼한 맛과 활력 충전 — 생강과 과일이 어우러져 상큼하고 아침 피로 해소에 도움 됨</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>귀여운 용기 디자인 — 미니 보틀 용기가 귀여워 자주 손이 감</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>신속하고 친절한 배송 — 배송이 빠르고 안내문이 친절함</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>생강 맛 호불호 — 생강 향과 맛이 강해 사람에 따라 호불호가 갈릴 수 있음</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
     </row>
@@ -3937,12 +3649,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
           <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -3979,14 +3691,14 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
+          <t>센트룸</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>옵티젠</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>센트룸</t>
-        </is>
-      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>뉴트리포유</t>
@@ -3994,12 +3706,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>닥터블릿</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
         </is>
       </c>
     </row>
@@ -4036,14 +3748,14 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
+          <t>[센트룸] 맛있는 멀티비타민 미네랄 멀티구미 (80구미)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>"한국인 맞춤 명품 비타민" 옵티젠 이뮨 멀티비타민&amp;미네랄 30입 / 1박스</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[센트룸] 맛있는 멀티비타민 미네랄 멀티구미 (80구미)</t>
-        </is>
-      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
@@ -4051,12 +3763,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
+          <t>'성별 맞춤 설계' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>'성별 맞춤 설계' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
     </row>
@@ -4104,13 +3816,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16146</v>
+        <v>16147</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15479</v>
+        <v>15480</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3370</v>
+        <v>3371</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>796</v>
@@ -4119,135 +3831,54 @@
         <v>1696</v>
       </c>
       <c r="H7" s="3" t="n">
+        <v>6489</v>
+      </c>
+      <c r="I7" s="3" t="n">
         <v>214</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>6489</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>8729</v>
       </c>
       <c r="K7" s="3" t="n">
+        <v>773</v>
+      </c>
+      <c r="L7" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="L7" s="3" t="n">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+    </row>
+    <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>피로 회복 및 활력 충전 — 피곤할 때 섭취 시 활력이 생기고 컨디션 관리에 도움이 됨
-선물용으로 높은 만족도 — 30대 생일이나 명절 선물로 주고받기 적합함
-간편한 복용 방식 — 액상과 정제를 함께 섭취하는 구성이라 간편함</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>빠른 배송 및 깔끔한 포장 — 연휴 기간에도 배송이 빠르고 패키지가 고급스러움
-피로 회복 효과 — 시험 준비나 피로할 때 섭취 시 피로 해소에 도움이 됨
-휴대 및 복용 편의성 — 하나씩 들고 다니며 부담 없이 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>활력 증진 및 피로 개선 — 힘든 일을 할 때 생기가 생기고 피곤함이 줄어듦
-선물 만족도 — 가족이나 지인에게 선물하기 좋으며 받는 사람의 만족도가 높음
-쿠폰 할인 혜택 — 할인 쿠폰을 적용하여 알뜰하게 구매 가능함</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>체력 방전 예방 — 육아나 힘든 일 전에 먹으면 하루 종일 에너지를 유지하는 데 도움 됨
-개별 포장의 편리성 — 한 포씩 포장되어 가방이나 책상에 두고 챙겨 먹기 편함
-빠른 배송과 가격 — 배송이 빠르고 저렴한 가격에 구매 가능함</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>빠른 활력 충전 — 섭취 후 피로가 감소하고 즉각적인 활력이 느껴짐
-상큼한 맛과 편의성 — 맛이 상큼해서 목넘김이 좋고 마시기 편리함
-신속한 배송 — 주문 후 배송이 매우 빠르게 도착함</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>정성스러운 선물 포장 — 선물 패키징이 정성스럽고 깔끔하여 받는 기분이 좋음
-피로 개선 효과 — 꾸준히 섭취 시 덜 피로하고 컨디션 유지에 좋음
-간편한 1일 섭취 — 캡슐과 액상을 한 번에 복용할 수 있어 사무실 등에서 챙겨 먹기 편함</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>맛있는 젤리 제형 — 마이구미처럼 맛있고 물 없이 편하게 섭취 가능함
-꾸준한 복용 편의성 — 거부감 없는 맛과 제형 덕분에 매일 잊지 않고 챙겨 먹기 좋음
-귀여운 패키지 포장 — 포장이 귀엽고 깔끔하여 부담 없는 선물로 적합함</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>물 없는 간편 섭취 — 액상과 정제가 함께 있어 물 없이 어디서나 먹기 편함
-활력 증진 효과 — 피곤할 때 섭취 시 에너지가 생기는 느낌을 받음
-개별 포장 및 디자인 — 휴대하기 편한 개별 포장에 케이스 디자인이 예쁨</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>간편한 복용과 휴대성 — 먹기 편리하며 챙겨 다니기 용이함
-빠른 배송 및 쇼핑백 증정 — 연휴에도 배송이 빠르고 쇼핑백이 포함되어 선물하기 좋음
-넉넉한 용량 구성 — 한 달 분량의 알찬 구성으로 든든하게 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>성별 맞춤 선택 — 남성용과 여성용을 선택하여 구매할 수 있음
-피로 완화 지속성 — 꾸준히 먹으면 피로감이 줄어들고 활력이 오래 유지됨
-휴대 및 복용 편의성 — 휴대하기 편하고 챙겨 먹기 간편함</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>가격 부담 — 매일 장기간 섭취하기에는 가격이 다소 부담스러움</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>쇼핑백 상태 불량 — 선물용으로 함께 제공된 쇼핑백의 품질이 불량함</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>배송 요청 사항 미반영 — 관리실 위탁 요청에도 문 앞에 배송되어 아쉬움</t>
-        </is>
-      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>포장재 오염 상태 — 택배 상자와 쇼핑백에 먼지가 묻어 도착함
-밀봉 스티커 훼손 — 스티커가 반쯤 떼어져 있고 손자국과 이물질이 남아 있음</t>
-        </is>
-      </c>
+      <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>알약 크기 부담 — 기존 제품 대비 알약 크기가 커서 삼키기 다소 힘듦</t>
-        </is>
-      </c>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -4282,14 +3913,14 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
+          <t>24,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
           <t>59,900원</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>24,000원</t>
-        </is>
-      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>19,900원</t>
@@ -4297,12 +3928,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
+          <t>59,800원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
           <t>52,900원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>59,800원</t>
         </is>
       </c>
     </row>
@@ -4470,22 +4101,22 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>피부/미용</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -4527,22 +4158,22 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
+          <t>알디콤</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
           <t>셀렉스</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>아일로</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>익스트림</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>알디콤</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -4584,22 +4215,22 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
           <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>아일로 타입1 콜라겐 비오틴 앰플 14일분 오간자 에디션 (고급 오간자 패키징 + 선물용 쇼핑백)</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -4652,150 +4283,69 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>152</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>104</v>
       </c>
       <c r="H19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="I19" s="3" t="n">
         <v>215</v>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="J19" s="3" t="n">
         <v>759</v>
       </c>
-      <c r="J19" s="3" t="n">
+      <c r="K19" s="3" t="n">
         <v>1534</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>18</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="20" ht="90" customHeight="1">
+    <row r="20">
       <c r="B20" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>고급스러운 포장 — 틴케이스와 보자기 등 패키지가 매우 예쁘고 정성스러움
-비리지 않은 맛 — 특유의 비린 맛이 없고 상큼해서 맛이 좋음
-낱개 앰플 섭취 편의 — 앰플 형태로 하나씩 따서 간편하게 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>소화 촉진 및 속 편안함 — 식후 복용 시 소화에 도움이 되고 속이 편안해짐
-부담 없는 맛 — 거부감이나 불편함이 없는 고구마 맛임
-빠른 배송과 풍부한 사은품 — 배송이 빠르고 추가 사은품 구성이 좋음</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>높은 포만감과 맛 — 하나만 먹어도 포만감이 크고 맛이 좋음
-다양한 구성과 사은품 — 여러 종류를 맛볼 수 있으며 증정 보냉백 디자인이 예쁨
-할인 혜택과 빠른 발송 — 할인 행사로 가격 만족도가 높고 발송이 빠름</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>뛰어난 가성비 — 할인가로 구매 시 가성비가 매우 훌륭함
-부드러운 식감과 다양한 맛 — 닭가슴살이 부드럽고 종류가 다양해 질리지 않음
-꼼꼼한 포장과 배송 — 포장 상태가 꼼꼼하며 빠르게 도착함</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>맛있는 베리말차 맛 — 효소가 고소하고 맛있어 꾸준히 먹기 좋음
-더부룩함 개선 — 식후 복용 시 더부룩함이 줄어들고 속이 편안해짐
-만족스러운 사은품 구성 — 포토카드 및 단백질바 증정품 구성이 우수함</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>비리지 않은 깔끔한 맛 — 단백질 특유의 텁텁함이나 비린 맛없이 달달하고 깔끔함
-운동 후 영양 보충 — 운동 후나 허기질 때 간편하게 챙겨 먹기 적합함
-빠른 배송 서비스 — 배송이 빠르고 증정품 서비스가 제공됨</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>고급스러운 패키지 — 포장이 예쁘고 케이스 디자인이 고급스러움
-상큼하고 맛있는 음료 제형 — 새콤하고 맛있어서 약을 싫어하는 사람도 먹기 편함
-선물용 만족도 — 받았을 때 기분 좋은 선물용 구성임</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>체감 피로 개선 — 아침 복용 및 운동 전 섭취 시 피로감이 줄고 활력이 생김
-알찬 영양제 조합 — 아르기닌과 밀크씨슬 또는 마카를 한 번에 챙길 수 있음
-쇼핑백 증정 — 쇼핑백이 포함되어 있어 선물용으로 전달하기 깔끔함</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>고급스러운 선물 세트 포장 — 보라색 패키지와 쇼핑백 포장이 고급스러움
-숙취 완화 효과 — 음주 전후 섭취 시 다음 날 피로와 숙취가 줄어듦
-스틱형 휴대성 — 소형 스틱형 개별 포장이라 물 없이 휴대 및 섭취가 간편함</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>상큼한 맛과 활력 충전 — 생강과 과일이 어우러져 상큼하고 아침 피로 해소에 도움 됨
-귀여운 용기 디자인 — 미니 보틀 용기가 귀여워 자주 손이 감
-신속하고 친절한 배송 — 배송이 빠르고 안내문이 친절함</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>비싼 가격대 — 가격대가 다소 높은 편이며 점차 인상됨</t>
-        </is>
-      </c>
+      <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>오배송 문제 — 주문한 구성과 달리 일부 제품이 누락되거나 중복 배송됨
-포장 터짐 및 헐렁함 — 제품 일부가 터져 소스가 묻거나 진공 포장이 불량함</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>배송 중 해동 발생 — 배송 도착 시 제품이 모두 녹아서 도착함</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>배송 지연 및 사은품 하자 — 배송이 다소 늦고 초기 증정 포토카드에 하자가 있었음</t>
-        </is>
-      </c>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>생강 맛 호불호 — 생강 향과 맛이 강해 사람에 따라 호불호가 갈릴 수 있음</t>
-        </is>
-      </c>
+      <c r="L21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="B22" s="1" t="inlineStr">
@@ -4830,22 +4380,22 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
+          <t>33,200원</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
           <t>28,900원</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>32,900원</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>25,900원</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>33,200원</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -5040,7 +4590,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5048,12 +4598,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
+          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -5063,35 +4613,23 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000203&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260422/qm625V7JKEa8Iu7GrFAf987253276_00_01qm625V7JKEa8Iu7GrFAf.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251202/7FdyxsWTlcbRJnDROGoC600000203_00_007FdyxsWTlcbRJnDROGoC.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>701</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>우수한 가성비 — 가격 대비 성능과 구성이 매우 훌륭함</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>운동 수행 도움 — 운동할 때 복용하면 컨디션 관리에 도움이 됨</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>휴대 편의성 및 빠른 배송 — 가방에 넣어 다니기 좋고 배송이 빠름</t>
-        </is>
-      </c>
+        <v>1632</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -5099,7 +4637,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5107,55 +4645,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>[식후 혈당] 동화 배러크런치 바나바 요구르트맛 30정 10일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601678608&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260825/oxNqPxCfU3Tre5j0PQQk601678608_00_02oxNqPxCfU3Tre5j0PQQk.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J3" t="n">
-        <v>2743</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>속쓰림 없는 복용 — 속쓰림 없이 하루 한 정씩 부담 없이 챙겨 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>뛰어난 가성비 — 가격이 저렴하여 꾸준히 재구매하기 적합함</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>깔끔한 포장과 빠른 배송 — 포장이 깔끔하고 배송이 빠르게 도착함</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>잦은 품절 — 품절이 자주 발생하여 구매 타이밍을 기다려야 함</t>
-        </is>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -5170,12 +4692,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[옥수수수염＆호박] 동국제약 맛있는 센텔라 공주캔디 20정 20일분</t>
+          <t>[혈액 생성] 동화약품 배러크런치 철분 사과맛 30정 10일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5185,47 +4707,31 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911213&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601678607&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260907/E3CpURjLLswf9MgzRChF610911213_00_01E3CpURjLLswf9MgzRChF.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260825/1a3CLvRrBJMActwA3NW5601678607_00_021a3CLvRrBJMActwA3NW5.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>89</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>붓기 완화 체감 — 섭취 시 붓기 빠지는 데 효과를 느낌</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>상큼한 간식용 캔디 — 상큼해서 간식처럼 먹거나 주변에 나누어 주기 좋음</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>인위적인 향 호불호 — 복숭아 향이 다소 인위적이라 호불호가 갈림</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>불명확한 효과 체감 — 드라마틱한 효과를 느끼기에는 부족함이 있음</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5233,45 +4739,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>안국약품 토비콤 루테인 지아잔틴 24캡슐</t>
+          <t>[정상 면역] 동화약품 배러크런치 아연 청포도맛 30정 10일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=611982830&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601678606&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250623/xCRETYTkHbPblUcjT18I611982830_00_00xCRETYTkHbPblUcjT18I.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260825/9arKLwQMyanllW5dsWAc601678606_00_029arKLwQMyanllW5dsWAc.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J5" t="n">
-        <v>1090</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>높은 가성비 — 가격이 저렴하여 떨어질 때마다 꾸준히 재구매함</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>복합 성분 함유 — 지아잔틴 외에도 다양한 비타민이 함유되어 있음</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -5280,7 +4778,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5288,45 +4786,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 콘드로이친 30정 30일분</t>
+          <t>[항산화] 동화약품 배러크런치C 레몬맛 30정 10일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000152&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601678604&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/b7btdcjQN0UwyzjBmHvY600000152_00_00b7btdcjQN0UwyzjBmHvY.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260825/GVr6GsoojIJO6UtcBMHG601678604_00_02GVr6GsoojIJO6UtcBMHG.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>1212</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>간편한 섭취 — 매일 한 알씩 챙겨 먹기 안전하고 편리함</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>영양제 구매 편리성 — 다양한 영양제를 한 번에 편하게 구매할 수 있음</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -5343,12 +4833,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대웅제약 비타민B 30정 30일분</t>
+          <t>동화 부채표 편안활 5포 5일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5358,47 +4848,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000129&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618636&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5QghHD5oyZssCfnGZbzA600000129_00_005QghHD5oyZssCfnGZbzA.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260414/Rr7eEkWvVmX4lCcRcfuW601618636_00_00Rr7eEkWvVmX4lCcRcfuW.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>2243</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>뛰어난 가성비 — 출근 시 매일 챙겨 먹기 부담 없는 가성비 제품임</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>단일 성분 구성 — 비타민B 단일 성분으로 깔끔하게 구성되어 있음</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>빠른 배송 — 주문 후 배송이 빠름</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>함량 대비 가격 아쉬움 — 고함량 제품 대비 가격이나 구성 면에서 다소 아쉬움이 있음</t>
-        </is>
-      </c>
+        <v>3466</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5406,45 +4880,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>종근당건강 락토핏 골드</t>
+          <t>동화 바이마그랩 마그네슘 식이섬유 5포 5일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580521&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618642&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260522/0jgRGoNZEcwwrbTgrqVw591580521_00_000jgRGoNZEcwwrbTgrqVw.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260406/wJCESiflDyulw8oZ8pW1601618642_00_00wJCESiflDyulw8oZ8pW1.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>1642</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>소량 저렴 구매 가능 — 필요한 만큼 적은 용량으로 싸게 살 수 있어 좋음</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>높은 구매 만족도 — 제품 품질이 무난하고 만족스러워 재구매함</t>
-        </is>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -5453,7 +4919,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5461,45 +4927,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>종근당건강 눈건강엔 루테인지아잔틴</t>
+          <t>[뼈건강] 동화약품 배러크런치D 블루베리맛 30정 10일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580541&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601678605&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250430/yuK2zGjcuX8RmMDP9k9P591580541_00_00yuK2zGjcuX8RmMDP9k9P.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260825/7MsbLqZDKF4lyLv3ucON601678605_00_027MsbLqZDKF4lyLv3ucON.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="n">
-        <v>1742</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>가격 대비 성능 — 가격이 저렴하고 가성비가 양호함</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>눈 건강 관리 용이 — 매일 잊지 않고 챙겨 먹기 좋음</t>
-        </is>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -5508,7 +4966,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5516,50 +4974,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>유한양행 장건강 생유산균 30캡슐 30일분</t>
+          <t>동국 맛있는 샐러드 미니볼 15포 15일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651649&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910891&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260325/RN6BLb2wWdxkL0nu9aVK600651649_00_00RN6BLb2wWdxkL0nu9aVK.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260312/tgDz0oHoOLB3gj3BLgFd610910891_00_01tgDz0oHoOLB3gj3BLgFd.png</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>1676</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>장 건강 개선 — 꾸준히 복용 시 장이 편안해지는 효과를 봄</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>캡슐형 섭취 편의 — 가루 형태보다 캡슐 형태라 복용하기 편함</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>저렴한 가격 — 가격이 싸서 부담 없이 시작하기 좋음</t>
-        </is>
-      </c>
+        <v>2217</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -5575,50 +5021,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[김우빈 PICK] 종근당건강 아임비타 비타민B 2000 30정 30일분</t>
+          <t>[에너지] 동화약품 배러크런치B 오렌지맛 30정 10일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581091&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601678603&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260601/30NEHOm4dIOnmUVwUKLJ591581091_00_0030NEHOm4dIOnmUVwUKLJ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260825/1iaDXDZs14qWRuWOkuNr601678603_00_021iaDXDZs14qWRuWOkuNr.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J11" t="n">
-        <v>527</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>저렴한 가격과 가성비 — 약국보다 저렴하여 가성비가 훌륭함</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>피로 축적 완화 — 하루 한 알 복용으로 피로가 덜 쌓이는 효과가 있음</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>구매 및 픽업 편의성 — 편하게 구매 가능하며 픽업 안내가 빠름</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -5734,47 +5168,47 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>비타민C/항산화</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5791,52 +5225,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>동화약품</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>동화약품</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>동화약품</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>동화약품</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>동화약품</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>동화약품</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>안국약품</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>유한양행</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>동화약품</t>
         </is>
       </c>
     </row>
@@ -5848,52 +5282,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
+          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>[식후 혈당] 동화 배러크런치 바나바 요구르트맛 30정 10일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[옥수수수염＆호박] 동국제약 맛있는 센텔라 공주캔디 20정 20일분</t>
+          <t>[혈액 생성] 동화약품 배러크런치 철분 사과맛 30정 10일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>안국약품 토비콤 루테인 지아잔틴 24캡슐</t>
+          <t>[정상 면역] 동화약품 배러크런치 아연 청포도맛 30정 10일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 콘드로이친 30정 30일분</t>
+          <t>[항산화] 동화약품 배러크런치C 레몬맛 30정 10일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민B 30정 30일분</t>
+          <t>동화 부채표 편안활 5포 5일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>종근당건강 락토핏 골드</t>
+          <t>동화 바이마그랩 마그네슘 식이섬유 5포 5일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>종근당건강 눈건강엔 루테인지아잔틴</t>
+          <t>[뼈건강] 동화약품 배러크런치D 블루베리맛 30정 10일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>유한양행 장건강 생유산균 30캡슐 30일분</t>
+          <t>동국 맛있는 샐러드 미니볼 15포 15일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[김우빈 PICK] 종근당건강 아임비타 비타민B 2000 30정 30일분</t>
+          <t>[에너지] 동화약품 배러크런치B 오렌지맛 30정 10일분</t>
         </is>
       </c>
     </row>
@@ -5907,31 +5341,31 @@
         <v>4.8</v>
       </c>
       <c r="D6" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>4.6</v>
-      </c>
       <c r="F6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7">
@@ -5941,133 +5375,65 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>701</v>
+        <v>1632</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2743</v>
+        <v>59</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1090</v>
+        <v>37</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1212</v>
+        <v>34</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2243</v>
+        <v>3466</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1642</v>
+        <v>509</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1742</v>
+        <v>31</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1676</v>
+        <v>2217</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>우수한 가성비 — 가격 대비 성능과 구성이 매우 훌륭함
-운동 수행 도움 — 운동할 때 복용하면 컨디션 관리에 도움이 됨
-휴대 편의성 및 빠른 배송 — 가방에 넣어 다니기 좋고 배송이 빠름</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>속쓰림 없는 복용 — 속쓰림 없이 하루 한 정씩 부담 없이 챙겨 먹기 좋음
-뛰어난 가성비 — 가격이 저렴하여 꾸준히 재구매하기 적합함
-깔끔한 포장과 빠른 배송 — 포장이 깔끔하고 배송이 빠르게 도착함</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>붓기 완화 체감 — 섭취 시 붓기 빠지는 데 효과를 느낌
-상큼한 간식용 캔디 — 상큼해서 간식처럼 먹거나 주변에 나누어 주기 좋음</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>높은 가성비 — 가격이 저렴하여 떨어질 때마다 꾸준히 재구매함
-복합 성분 함유 — 지아잔틴 외에도 다양한 비타민이 함유되어 있음</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>간편한 섭취 — 매일 한 알씩 챙겨 먹기 안전하고 편리함
-영양제 구매 편리성 — 다양한 영양제를 한 번에 편하게 구매할 수 있음</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>뛰어난 가성비 — 출근 시 매일 챙겨 먹기 부담 없는 가성비 제품임
-단일 성분 구성 — 비타민B 단일 성분으로 깔끔하게 구성되어 있음
-빠른 배송 — 주문 후 배송이 빠름</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>소량 저렴 구매 가능 — 필요한 만큼 적은 용량으로 싸게 살 수 있어 좋음
-높은 구매 만족도 — 제품 품질이 무난하고 만족스러워 재구매함</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>가격 대비 성능 — 가격이 저렴하고 가성비가 양호함
-눈 건강 관리 용이 — 매일 잊지 않고 챙겨 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>장 건강 개선 — 꾸준히 복용 시 장이 편안해지는 효과를 봄
-캡슐형 섭취 편의 — 가루 형태보다 캡슐 형태라 복용하기 편함
-저렴한 가격 — 가격이 싸서 부담 없이 시작하기 좋음</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>저렴한 가격과 가성비 — 약국보다 저렴하여 가성비가 훌륭함
-피로 축적 완화 — 하루 한 알 복용으로 피로가 덜 쌓이는 효과가 있음
-구매 및 픽업 편의성 — 편하게 구매 가능하며 픽업 안내가 빠름</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>잦은 품절 — 품절이 자주 발생하여 구매 타이밍을 기다려야 함</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>인위적인 향 호불호 — 복숭아 향이 다소 인위적이라 호불호가 갈림
-불명확한 효과 체감 — 드라마틱한 효과를 느끼기에는 부족함이 있음</t>
-        </is>
-      </c>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>함량 대비 가격 아쉬움 — 고함량 제품 대비 가격이나 구성 면에서 다소 아쉬움이 있음</t>
-        </is>
-      </c>
+      <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
@@ -6086,7 +5452,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -6096,12 +5462,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -6111,22 +5477,22 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
     </row>
@@ -6313,27 +5679,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
+          <t>[TWS 띠부씰 증정] 미에로화이바 브이캔디 20정 기획</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>딥트3일</t>
+          <t>미에로화이바</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16,000원</t>
+          <t>19,800원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000211396&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000268343&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021139617ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026834303ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -6348,7 +5714,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -6356,50 +5722,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[9월 올영픽/급찐급빠] 칼로 스탑/컨트롤 PLUS 15포+15포 (+폼폼푸린 키링) / 더블기획 3종</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>칼로(Kalo)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31,900원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000243670&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024367015ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>8285</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>만족스러운 기획 증정품 — 키링이나 포토카드 등 기획 사은품 구성이 좋음</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>넉넉한 더블 기획 용량 — 60캡슐 구성으로 두 달 동안 충분히 복용 가능함</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>1일 1캡슐 간편 복용 — 아침 공복에 물과 함께 한 알씩 챙겨 먹기 편리함</t>
-        </is>
-      </c>
+        <v>12103</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -6415,50 +5769,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>25472</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>질과 장 더블 케어 — 질 건강과 장 건강을 한 번에 관리할 수 있음</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>작은 캡슐 크기 — 캡슐 사이즈가 작고 가벼워 목넘김이 매우 수월함</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>귀여운 캐릭터 콜라보 — 포켓몬 에디션 및 카드케이스 굿즈 구성이 매력적임</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -6466,7 +5804,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6474,50 +5812,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>39,800원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>524</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>체지방과 장 건강 동시 케어 — 다이어트 시 체지방 감소와 장 건강을 함께 챙길 수 있음</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>상큼한 요거트 맛 — 맛이 상큼한 요거트 맛이라 매일 먹기 편함</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>파격적인 할인 혜택 — 100원딜 및 할인 쿠폰을 통해 저렴하게 구매 가능함</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -6533,50 +5855,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[9월 올영픽/품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>닥터아돌</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000218073&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021807373ko.png?l=ko</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6470</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>3중 복합 기능성 케어 — 녹차추출물 카테킨과 비타민 C, D를 한 번에 케어함</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>식후 체지방 관리 — 고칼로리 음식 섭취 후 챙겨 먹는 식후 루틴으로 좋음</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>한정판 캐릭터 키링 증정 — 시나모롤 틴케이스 키링 사은품이 포함되어 있음</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -6584,7 +5890,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6592,27 +5898,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[행자PICK/~10/1특가] 락티브 이노시톨 탱글 젤리/컬리케일/이노시톨 기획세트(+질유래 유산균 10캡슐)</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>락티브</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=B000000244315&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/B00000024431506ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -6627,7 +5933,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6635,31 +5941,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[9월 올영픽/급찐급빠] 칼로 스탑/컨트롤 PLUS 15포+15포 (+폼폼푸린 키링) / 더블기획 3종</t>
+          <t>[9월 올영픽/김우빈PICK] 아임비타 멀티비타민 이뮨샷 12입 (+포차코 메쉬백) (12일분)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>칼로(Kalo)</t>
+          <t>아임비타</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>26,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000243670&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000249166&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024367015ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A000000249166123ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>11014</v>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
@@ -6678,31 +5988,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[TWS 띠부씰 증정] 미에로화이바 브이캔디 20정 기획</t>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>미에로화이바</t>
+          <t>씨제이웰케어</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19,800원</t>
+          <t>5,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000268343&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026834303ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786106ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>18935</v>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -6721,31 +6035,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>39,800원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>526</v>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
@@ -6756,7 +6074,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6764,31 +6082,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
+          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>코자아</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>26,000원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000236755&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023675540ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>26875</v>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
@@ -6912,47 +6234,47 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -6964,52 +6286,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>딥트3일</t>
+          <t>미에로화이바</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>칼로(Kalo)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>덴프스</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>지노마스터</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>멜라메이트</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>아임비타</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>씨제이웰케어</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>프로뉴트리션</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>닥터아돌</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>락티브</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>칼로(Kalo)</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>미에로화이바</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>푸드올로지</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>코자아</t>
         </is>
       </c>
     </row>
@@ -7021,52 +6343,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
+          <t>[TWS 띠부씰 증정] 미에로화이바 브이캔디 20정 기획</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>[9월 올영픽/급찐급빠] 칼로 스탑/컨트롤 PLUS 15포+15포 (+폼폼푸린 키링) / 더블기획 3종</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽/김우빈PICK] 아임비타 멀티비타민 이뮨샷 12입 (+포차코 메쉬백) (12일분)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽/품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[행자PICK/~10/1특가] 락티브 이노시톨 탱글 젤리/컬리케일/이노시톨 기획세트(+질유래 유산균 10캡슐)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽/급찐급빠] 칼로 스탑/컨트롤 PLUS 15포+15포 (+폼폼푸린 키링) / 더블기획 3종</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>[TWS 띠부씰 증정] 미에로화이바 브이캔디 20정 기획</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
         </is>
       </c>
     </row>
@@ -7078,22 +6400,24 @@
       </c>
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="F6" s="3" t="n">
+      <c r="J6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K6" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="L6" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="1" t="inlineStr">
@@ -7103,58 +6427,36 @@
       </c>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="n">
-        <v>8285</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>25472</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>524</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>6470</v>
-      </c>
+        <v>12103</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+      <c r="I7" s="3" t="n">
+        <v>11014</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>18935</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>526</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>26875</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>만족스러운 기획 증정품 — 키링이나 포토카드 등 기획 사은품 구성이 좋음
-넉넉한 더블 기획 용량 — 60캡슐 구성으로 두 달 동안 충분히 복용 가능함
-1일 1캡슐 간편 복용 — 아침 공복에 물과 함께 한 알씩 챙겨 먹기 편리함</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>질과 장 더블 케어 — 질 건강과 장 건강을 한 번에 관리할 수 있음
-작은 캡슐 크기 — 캡슐 사이즈가 작고 가벼워 목넘김이 매우 수월함
-귀여운 캐릭터 콜라보 — 포켓몬 에디션 및 카드케이스 굿즈 구성이 매력적임</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>체지방과 장 건강 동시 케어 — 다이어트 시 체지방 감소와 장 건강을 함께 챙길 수 있음
-상큼한 요거트 맛 — 맛이 상큼한 요거트 맛이라 매일 먹기 편함
-파격적인 할인 혜택 — 100원딜 및 할인 쿠폰을 통해 저렴하게 구매 가능함</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>3중 복합 기능성 케어 — 녹차추출물 카테킨과 비타민 C, D를 한 번에 케어함
-식후 체지방 관리 — 고칼로리 음식 섭취 후 챙겨 먹는 식후 루틴으로 좋음
-한정판 캐릭터 키링 증정 — 시나모롤 틴케이스 키링 사은품이 포함되어 있음</t>
-        </is>
-      </c>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
@@ -7186,52 +6488,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>16,000원</t>
+          <t>19,800원</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t>16,900원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>31,900원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>27,400원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>16,900원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>26,900원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>5,900원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>39,800원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>26,900원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>25,900원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>16,900원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>19,800원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>17,900원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>26,000원</t>
         </is>
       </c>
     </row>
@@ -7319,7 +6621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7370,38 +6672,38 @@
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D3" t="n">
         <v>8</v>
       </c>
-      <c r="C3" t="n">
-        <v>20</v>
-      </c>
-      <c r="D3" t="n">
-        <v>5</v>
-      </c>
       <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
         <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -7411,13 +6713,13 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -7427,25 +6729,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -7455,10 +6757,10 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
         <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -7467,7 +6769,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -7477,19 +6779,19 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -7511,7 +6813,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -7521,12 +6823,34 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="n">
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>0</v>
       </c>
     </row>
